--- a/trades/by_strategy/live_breakout_and_retest.xlsx
+++ b/trades/by_strategy/live_breakout_and_retest.xlsx
@@ -9,15 +9,21 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Breakout &amp; Retest (Live)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Breakout &amp; Retest (Live)'!$A$1:$AA$13</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="+0.00;-0.00;0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;Rs &quot;#,##0;[Red]-&quot;Rs &quot;#,##0;&quot;Rs &quot;0"/>
+    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%;0.0%"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +31,46 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +78,89 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,17 +526,1417 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="65" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>No live trades recorded for this strategy</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pool / Setup</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Entry Spot</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Stop Spot</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Target Spot</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Pts</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Exit Spot</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Exit Time</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Exit Reason</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>R-Multiple</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Expiry</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Entry Premium</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Exit Premium</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Capital Deployed</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Exit Value</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Est P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ROI %</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Lots</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>TARGET HIT (3R)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>22787.2</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>22739.35</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>22930.75</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>22930.75</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>143.55</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY 22900 CE</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>94.22</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>159.33</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>18373</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>31069</v>
+      </c>
+      <c r="V2" s="7" t="n">
+        <v>12597</v>
+      </c>
+      <c r="W2" s="8" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>09:35 breakout: 5m high 22,771.55 cleared PDH 22,757.80 | 09:40 retest: 5m low 22,748.55 tested PDH 22,757.80 as support | 09:50 confirmation: 5m close 22,787.20 held above PDH and VWAP</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>STOPPED OUT (-1R)</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>23109.55</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>23072.2</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>23221.6</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="K3" s="11" t="n">
+        <v>23072.2</v>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="n">
+        <v>-37.35</v>
+      </c>
+      <c r="O3" s="12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>NIFTY 23200 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="R3" s="11" t="n">
+        <v>81.22</v>
+      </c>
+      <c r="S3" s="11" t="n">
+        <v>67.58</v>
+      </c>
+      <c r="T3" s="13" t="n">
+        <v>15838</v>
+      </c>
+      <c r="U3" s="13" t="n">
+        <v>13178</v>
+      </c>
+      <c r="V3" s="14" t="n">
+        <v>-2733</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>-17.3</v>
+      </c>
+      <c r="X3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y3" s="9" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z3" s="10" t="inlineStr">
+        <is>
+          <t>10:15 breakout: 5m high 23,094.60 cleared OR-30H 23,076.10 | 10:50 retest: 5m low 23,082.25 tested OR-30H 23,076.10 as support | 11:00 confirmation: 5m close 23,109.55 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>TRAILED (+0.99R)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>23088.9</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>23054.45</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>23192.25</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>23123.05</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Structure Trail</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY 23200 CE</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>85.19</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>14303</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <v>16612</v>
+      </c>
+      <c r="V4" s="7" t="n">
+        <v>2232</v>
+      </c>
+      <c r="W4" s="8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>10:15 breakout: 5m high 23,094.60 cleared PDH 23,056.20 | 11:10 retest: 5m low 23,066.70 tested PDH 23,056.20 as support | 11:15 confirmation: 5m close 23,088.90 held above PDH and VWAP</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>TRAILED (+0.38R)</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>22945.55</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>22983.55</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>22831.55</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>22931.3</v>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>NIFTY 22850 PE</t>
+        </is>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R5" s="11" t="n">
+        <v>147.75</v>
+      </c>
+      <c r="S5" s="11" t="n">
+        <v>153.49</v>
+      </c>
+      <c r="T5" s="13" t="n">
+        <v>28811</v>
+      </c>
+      <c r="U5" s="13" t="n">
+        <v>29931</v>
+      </c>
+      <c r="V5" s="17" t="n">
+        <v>1017</v>
+      </c>
+      <c r="W5" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z5" s="10" t="inlineStr">
+        <is>
+          <t>12:05 breakdown: 5m low 22,948.75 breached OR-30L 22,970.85 | 12:10 retest: 5m high 22,978.55 tested OR-30L 22,970.85 as resistance | 12:15 confirmation: 5m close 22,945.55 held below OR-30L and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>PDL Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>22891.95</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>22932.2</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>22771.2</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>22891.95</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Breakeven</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY 22800 PE</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>148.32</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>147.96</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>28922</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <v>28852</v>
+      </c>
+      <c r="V6" s="20" t="n">
+        <v>-171</v>
+      </c>
+      <c r="W6" s="21" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>13:00 breakdown: 5m low 22,906.00 breached PDL 22,914.30 | 13:15 retest: 5m high 22,927.20 tested PDL 22,914.30 as resistance | 13:20 confirmation: 5m close 22,891.95 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>STOPPED OUT (-1R)</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>22936.05</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>22979.15</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>22848.25</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>22979.15</v>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="O7" s="12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>NIFTY 22850 PE</t>
+        </is>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R7" s="11" t="n">
+        <v>136.34</v>
+      </c>
+      <c r="S7" s="11" t="n">
+        <v>118.95</v>
+      </c>
+      <c r="T7" s="13" t="n">
+        <v>26586</v>
+      </c>
+      <c r="U7" s="13" t="n">
+        <v>23195</v>
+      </c>
+      <c r="V7" s="14" t="n">
+        <v>-3483</v>
+      </c>
+      <c r="W7" s="15" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="X7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z7" s="10" t="inlineStr">
+        <is>
+          <t>10:10 breakdown: 5m low 22,950.90 breached OR-30L 22,981.35 | 10:15 retest: 5m high 22,974.15 tested OR-30L 22,981.35 as resistance | 10:20 confirmation: 5m close 22,936.05 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>TARGET HIT (3R)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>22818.45</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>22850.55</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>22722.15</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>22722.15</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY 22700 PE</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>121.21</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>162.55</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>23636</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <v>31697</v>
+      </c>
+      <c r="V8" s="7" t="n">
+        <v>7959</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>11:40 breakdown: 5m low 22,839.70 breached PDL 22,845.25 | 11:45 retest: 5m high 22,841.90 tested PDL 22,845.25 as resistance | 11:55 confirmation: 5m close 22,818.45 held below PDL and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>TRAILED (+0.89R)</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>22712.95</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>22671.3</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>22900.38</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>22749.9</v>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>Structure Trail</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="O9" s="16" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>NIFTY 22800 CE</t>
+        </is>
+      </c>
+      <c r="Q9" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R9" s="11" t="n">
+        <v>129.77</v>
+      </c>
+      <c r="S9" s="11" t="n">
+        <v>145.68</v>
+      </c>
+      <c r="T9" s="13" t="n">
+        <v>25305</v>
+      </c>
+      <c r="U9" s="13" t="n">
+        <v>28408</v>
+      </c>
+      <c r="V9" s="17" t="n">
+        <v>3004</v>
+      </c>
+      <c r="W9" s="18" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="X9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="9" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z9" s="10" t="inlineStr">
+        <is>
+          <t>10:25 breakout: 5m high 22,742.50 cleared OR-30H 22,690.45 | 10:50 retest: 5m low 22,676.30 tested OR-30H 22,690.45 as support | 10:55 confirmation: 5m close 22,712.95 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>OR-30 Breakout [1M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.59R)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>22739.75</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>22696.5</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>22869.5</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>22869.5</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Target (+3.0R Full Target Achieved)</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY 22850 CE</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>110.17</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="T10" s="6" t="n">
+        <v>28644</v>
+      </c>
+      <c r="U10" s="6" t="n">
+        <v>43955</v>
+      </c>
+      <c r="V10" s="7" t="n">
+        <v>15311</v>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>09:34 1M candle closed at 22,739.75 clearing OR-30 high with volume expansion above VWAP. Exited on full target expansion to 22,869.50 (+58.89 pts / +3.59R).</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [15M Macro Structure]</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.47R)</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>22827.05</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>22782.3</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>22961.3</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>22958.2</v>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>Target 3 Hit (+3.0R Full Target / 15:14 IST Spot 22,958+)</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="O11" s="16" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>NIFTY 22950 CE</t>
+        </is>
+      </c>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R11" s="11" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="S11" s="11" t="n">
+        <v>158.61</v>
+      </c>
+      <c r="T11" s="13" t="n">
+        <v>25761</v>
+      </c>
+      <c r="U11" s="13" t="n">
+        <v>41239</v>
+      </c>
+      <c r="V11" s="17" t="n">
+        <v>15478</v>
+      </c>
+      <c r="W11" s="18" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z11" s="10" t="inlineStr">
+        <is>
+          <t>11:15 IST 15M breakout and retest of PDH held above VWAP. Reached full target at 15:14 IST (+59.53 pts / +3.47R). Realized +Rs 15,478.00.</t>
+        </is>
+      </c>
+      <c r="AA11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [5M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.14R)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>22980.7</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>22950.1</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>23072.5</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>23053.45</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>+3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY 23100 CE</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>78.67</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>114.32</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>20454</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>29723</v>
+      </c>
+      <c r="V12" s="7" t="n">
+        <v>9269</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Paper trading forward test executed on 5M timeframe. +3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>OR-30H Support Flip [5M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.34R)</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>23006.25</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>22974.75</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>23100.75</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>23053.1</v>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>+3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="O13" s="16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P13" s="10" t="inlineStr">
+        <is>
+          <t>NIFTY 23100 CE</t>
+        </is>
+      </c>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R13" s="11" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="S13" s="11" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="T13" s="13" t="n">
+        <v>16190</v>
+      </c>
+      <c r="U13" s="13" t="n">
+        <v>25610</v>
+      </c>
+      <c r="V13" s="17" t="n">
+        <v>9420</v>
+      </c>
+      <c r="W13" s="18" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="X13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" s="9" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z13" s="10" t="inlineStr">
+        <is>
+          <t>Paper trading forward test executed on 5M timeframe. +3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="AA13" s="10" t="inlineStr">
+        <is>
+          <t>paper</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AA13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>